--- a/product-definitions/spreadsheet/no2-concentration.xlsx
+++ b/product-definitions/spreadsheet/no2-concentration.xlsx
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -208,11 +208,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -309,7 +304,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1962,7 +1957,7 @@
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8" t="s">
         <v>19</v>
@@ -1975,7 +1970,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>20</v>
@@ -1988,7 +1983,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
@@ -2001,7 +1996,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
@@ -2014,7 +2009,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
@@ -2027,7 +2022,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>26</v>
@@ -2040,7 +2035,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>28</v>
@@ -2053,7 +2048,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="18" t="s">
         <v>30</v>
@@ -2066,7 +2061,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="10"/>
@@ -2075,7 +2070,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>35</v>
       </c>
@@ -2086,7 +2081,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
         <v>10</v>
@@ -2099,7 +2094,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
         <v>12</v>
@@ -2112,7 +2107,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>2</v>
@@ -2125,7 +2120,7 @@
       <c r="F33" s="10"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>19</v>
@@ -2138,7 +2133,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>20</v>
@@ -2151,7 +2146,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>22</v>
@@ -2164,7 +2159,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>23</v>
@@ -2177,7 +2172,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>25</v>
@@ -2190,7 +2185,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>26</v>
@@ -2203,7 +2198,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="s">
         <v>28</v>
@@ -2216,7 +2211,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="18" t="s">
         <v>30</v>
@@ -2229,7 +2224,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2238,7 +2233,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>38</v>
       </c>
@@ -2249,7 +2244,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
         <v>12</v>
@@ -2275,7 +2270,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>2</v>
@@ -2288,7 +2283,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
         <v>19</v>
@@ -2301,7 +2296,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8" t="s">
         <v>20</v>
@@ -2314,7 +2309,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8" t="s">
         <v>22</v>
@@ -2327,7 +2322,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>23</v>
@@ -2340,7 +2335,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
         <v>25</v>
@@ -2353,7 +2348,7 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>26</v>
@@ -2366,7 +2361,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8" t="s">
         <v>28</v>
@@ -2379,7 +2374,7 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="18" t="s">
         <v>30</v>
@@ -2392,11 +2387,11 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="24"/>
       <c r="E55" s="25"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>41</v>
       </c>
@@ -2404,7 +2399,7 @@
       <c r="C56" s="26"/>
       <c r="E56" s="25"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>10</v>
@@ -2414,7 +2409,7 @@
       </c>
       <c r="E57" s="25"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>12</v>
@@ -2424,7 +2419,7 @@
       </c>
       <c r="E58" s="25"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>2</v>
@@ -2434,7 +2429,7 @@
       </c>
       <c r="E59" s="25"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>19</v>
@@ -2442,7 +2437,7 @@
       <c r="C60" s="26"/>
       <c r="E60" s="25"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>20</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="E61" s="25"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="8" t="s">
         <v>44</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="E62" s="25"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="10" t="s">
         <v>46</v>
